--- a/tracking_forms/017_coronavirus_measures_checklist--tracking_forms.xlsx
+++ b/tracking_forms/017_coronavirus_measures_checklist--tracking_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -819,12 +819,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>temperature</t>
+          <t>temperature_2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Temperature</t>
+          <t>Temperature 2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -842,12 +842,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>employee_status</t>
+          <t>employee_status_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Employee Status</t>
+          <t>Employee Status 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>symptoms</t>
+          <t>symptoms_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Symptoms</t>
+          <t>Symptoms 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>contact_trace</t>
+          <t>contact_trace_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Contact Trace</t>
+          <t>Contact Trace 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -1248,7 +1248,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>employee_status_choices</t>
+          <t>employee_status_2_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1265,7 +1265,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>employee_status_choices</t>
+          <t>employee_status_2_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1282,7 +1282,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>symptoms_2_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1299,7 +1299,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>symptoms_choices</t>
+          <t>symptoms_2_choices</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1316,7 +1316,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>contact_trace_choices</t>
+          <t>contact_trace_2_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1333,7 +1333,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>contact_trace_choices</t>
+          <t>contact_trace_2_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
